--- a/packages/calculators/src/modules/test/16-lulucf/16.3-lulucf.xlsx
+++ b/packages/calculators/src/modules/test/16-lulucf/16.3-lulucf.xlsx
@@ -1,20 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators-internal/packages/calculators/src/modules/test/16-lulucf/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCB6AB13-2D3D-7448-95DF-ED3932972555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EDDE813-82A6-C24D-8B3D-191DAA241F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15220" yWindow="-19840" windowWidth="30240" windowHeight="18980" xr2:uid="{CC0FEAF9-C40F-694B-BCB9-117AFB86C05D}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{CC0FEAF9-C40F-694B-BCB9-117AFB86C05D}"/>
   </bookViews>
   <sheets>
     <sheet name="16.3.1.1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -650,6 +648,31 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="common"/>
+    </sheetNames>
+    <definedNames>
+      <definedName name="common_cn2o" refersTo="='common'!$B$4"/>
+    </definedNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="4">
+          <cell r="B4">
+            <v>1.57</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1063,8 +1086,8 @@
         <v>92</v>
       </c>
       <c r="V7">
-        <f>44/28</f>
-        <v>1.5714285714285714</v>
+        <f>[1]!common_cn2o</f>
+        <v>1.57</v>
       </c>
       <c r="Z7" s="6" t="s">
         <v>119</v>
@@ -1234,7 +1257,7 @@
       </c>
       <c r="N11">
         <f>$V$7</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="O11">
         <f>IF(D11="yes",1,0)</f>
@@ -1250,11 +1273,11 @@
       </c>
       <c r="R11">
         <f>(J11*L11+K11*M11)*$N$11</f>
-        <v>-6.2406666666666669E-3</v>
+        <v>-6.2349933333333343E-3</v>
       </c>
       <c r="S11">
         <f>I11*O11*P$11*Q$11*N$11</f>
-        <v>-2.3536228571428568E-3</v>
+        <v>-2.3514831999999998E-3</v>
       </c>
       <c r="Z11" s="6"/>
     </row>
@@ -1311,11 +1334,11 @@
       </c>
       <c r="R12">
         <f t="shared" ref="R12:R75" si="8">(J12*L12+K12*M12)*$N$11</f>
-        <v>-9.2753047619047613E-3</v>
+        <v>-9.266872666666667E-3</v>
       </c>
       <c r="S12">
         <f t="shared" ref="S12:S75" si="9">I12*O12*P$11*Q$11*N$11</f>
-        <v>-8.4437257142857148E-3</v>
+        <v>-8.4360496000000004E-3</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -1371,11 +1394,11 @@
       </c>
       <c r="R13">
         <f t="shared" si="8"/>
-        <v>-5.3617142857142856E-3</v>
+        <v>-5.3568400000000007E-3</v>
       </c>
       <c r="S13">
         <f t="shared" si="9"/>
-        <v>-1.7693657142857141E-3</v>
+        <v>-1.7677571999999999E-3</v>
       </c>
       <c r="W13" t="s">
         <v>5</v>
@@ -1437,11 +1460,11 @@
       </c>
       <c r="R14">
         <f t="shared" si="8"/>
-        <v>-4.6969999999999998E-3</v>
+        <v>-4.69273E-3</v>
       </c>
       <c r="S14">
         <f t="shared" si="9"/>
-        <v>-1.7714399999999998E-3</v>
+        <v>-1.7698295999999999E-3</v>
       </c>
       <c r="W14" t="s">
         <v>6</v>
@@ -1503,11 +1526,11 @@
       </c>
       <c r="R15">
         <f t="shared" si="8"/>
-        <v>-7.3150000000000003E-3</v>
+        <v>-7.3083500000000008E-3</v>
       </c>
       <c r="S15">
         <f t="shared" si="9"/>
-        <v>-2.7587999999999996E-3</v>
+        <v>-2.7562919999999996E-3</v>
       </c>
       <c r="W15" t="s">
         <v>7</v>
@@ -1569,11 +1592,11 @@
       </c>
       <c r="R16">
         <f t="shared" si="8"/>
-        <v>-6.8004444444444449E-3</v>
+        <v>-6.794262222222223E-3</v>
       </c>
       <c r="S16">
         <f t="shared" si="9"/>
-        <v>-2.5647390476190471E-3</v>
+        <v>-2.5624074666666663E-3</v>
       </c>
       <c r="W16" t="s">
         <v>8</v>
@@ -1635,11 +1658,11 @@
       </c>
       <c r="R17">
         <f t="shared" si="8"/>
-        <v>-1.6235388888888889E-2</v>
+        <v>-1.6220629444444447E-2</v>
       </c>
       <c r="S17">
         <f t="shared" si="9"/>
-        <v>-6.1230609523809524E-3</v>
+        <v>-6.1174945333333335E-3</v>
       </c>
       <c r="W17" t="s">
         <v>9</v>
@@ -1701,11 +1724,11 @@
       </c>
       <c r="R18">
         <f t="shared" si="8"/>
-        <v>-5.243333333333339E-4</v>
+        <v>-5.2385666666666735E-4</v>
       </c>
       <c r="S18">
         <f t="shared" si="9"/>
-        <v>-1.9774857142857165E-4</v>
+        <v>-1.9756880000000024E-4</v>
       </c>
       <c r="W18" t="s">
         <v>10</v>
@@ -1767,11 +1790,11 @@
       </c>
       <c r="R19">
         <f t="shared" si="8"/>
-        <v>-3.6746111111111159E-3</v>
+        <v>-3.6712705555555607E-3</v>
       </c>
       <c r="S19">
         <f t="shared" si="9"/>
-        <v>-1.3858533333333347E-3</v>
+        <v>-1.3845934666666681E-3</v>
       </c>
       <c r="W19" t="s">
         <v>11</v>
@@ -1833,11 +1856,11 @@
       </c>
       <c r="R20">
         <f t="shared" si="8"/>
-        <v>-3.1533333333333365E-3</v>
+        <v>-3.15046666666667E-3</v>
       </c>
       <c r="S20">
         <f t="shared" si="9"/>
-        <v>-1.1892571428571441E-3</v>
+        <v>-1.1881760000000013E-3</v>
       </c>
       <c r="W20" t="s">
         <v>12</v>
@@ -1899,11 +1922,11 @@
       </c>
       <c r="R21">
         <f t="shared" si="8"/>
-        <v>-4.7355000000000053E-3</v>
+        <v>-4.7311950000000057E-3</v>
       </c>
       <c r="S21">
         <f t="shared" si="9"/>
-        <v>-1.785960000000002E-3</v>
+        <v>-1.7843364000000022E-3</v>
       </c>
       <c r="W21" t="s">
         <v>13</v>
@@ -1965,11 +1988,11 @@
       </c>
       <c r="R22">
         <f t="shared" si="8"/>
-        <v>-1.0008777777777788E-2</v>
+        <v>-9.9996788888888997E-3</v>
       </c>
       <c r="S22">
         <f t="shared" si="9"/>
-        <v>-3.7747390476190515E-3</v>
+        <v>-3.7713074666666708E-3</v>
       </c>
       <c r="W22" t="s">
         <v>14</v>
@@ -2031,11 +2054,11 @@
       </c>
       <c r="R23">
         <f t="shared" si="8"/>
-        <v>-6.856055555555564E-3</v>
+        <v>-6.849822777777786E-3</v>
       </c>
       <c r="S23">
         <f t="shared" si="9"/>
-        <v>-2.5857123809523838E-3</v>
+        <v>-2.5833617333333365E-3</v>
       </c>
       <c r="W23" t="s">
         <v>15</v>
@@ -2097,11 +2120,11 @@
       </c>
       <c r="R24">
         <f t="shared" si="8"/>
-        <v>-2.1120000000000028E-3</v>
+        <v>-2.1100800000000029E-3</v>
       </c>
       <c r="S24">
         <f t="shared" si="9"/>
-        <v>-7.9652571428571518E-4</v>
+        <v>-7.9580160000000092E-4</v>
       </c>
       <c r="W24" t="s">
         <v>16</v>
@@ -2163,11 +2186,11 @@
       </c>
       <c r="R25">
         <f t="shared" si="8"/>
-        <v>-2.1144444444444473E-2</v>
+        <v>-2.112522222222225E-2</v>
       </c>
       <c r="S25">
         <f t="shared" si="9"/>
-        <v>-7.9744761904762002E-3</v>
+        <v>-7.9672266666666759E-3</v>
       </c>
       <c r="W25" t="s">
         <v>17</v>
@@ -2229,11 +2252,11 @@
       </c>
       <c r="R26">
         <f t="shared" si="8"/>
-        <v>-4.7630000000000059E-3</v>
+        <v>-4.7586700000000056E-3</v>
       </c>
       <c r="S26">
         <f t="shared" si="9"/>
-        <v>-1.7963314285714303E-3</v>
+        <v>-1.7946984000000018E-3</v>
       </c>
       <c r="W26" t="s">
         <v>18</v>
@@ -2295,11 +2318,11 @@
       </c>
       <c r="R27">
         <f t="shared" si="8"/>
-        <v>-2.1193333333333355E-3</v>
+        <v>-2.117406666666669E-3</v>
       </c>
       <c r="S27">
         <f t="shared" si="9"/>
-        <v>-7.9929142857142926E-4</v>
+        <v>-7.9856480000000069E-4</v>
       </c>
       <c r="W27" t="s">
         <v>19</v>
@@ -2361,11 +2384,11 @@
       </c>
       <c r="R28">
         <f t="shared" si="8"/>
-        <v>-2.3339555555555582E-2</v>
+        <v>-2.3318337777777805E-2</v>
       </c>
       <c r="S28">
         <f t="shared" si="9"/>
-        <v>-8.8023466666666775E-3</v>
+        <v>-8.7943445333333436E-3</v>
       </c>
       <c r="W28" t="s">
         <v>20</v>
@@ -2427,11 +2450,11 @@
       </c>
       <c r="R29">
         <f t="shared" si="8"/>
-        <v>-1.1152166666666678E-2</v>
+        <v>-1.1142028333333347E-2</v>
       </c>
       <c r="S29">
         <f t="shared" si="9"/>
-        <v>-4.2059600000000042E-3</v>
+        <v>-4.202136400000004E-3</v>
       </c>
       <c r="W29" t="s">
         <v>21</v>
@@ -2493,11 +2516,11 @@
       </c>
       <c r="R30">
         <f t="shared" si="8"/>
-        <v>-1.1165000000000026E-2</v>
+        <v>-1.1154850000000027E-2</v>
       </c>
       <c r="S30">
         <f t="shared" si="9"/>
-        <v>-4.2108000000000093E-3</v>
+        <v>-4.2069720000000093E-3</v>
       </c>
       <c r="W30" t="s">
         <v>22</v>
@@ -2559,11 +2582,11 @@
       </c>
       <c r="R31">
         <f t="shared" si="8"/>
-        <v>-1.0113277777777803E-2</v>
+        <v>-1.0104083888888914E-2</v>
       </c>
       <c r="S31">
         <f t="shared" si="9"/>
-        <v>-3.8141504761904843E-3</v>
+        <v>-3.8106830666666753E-3</v>
       </c>
       <c r="W31" t="s">
         <v>23</v>
@@ -2625,11 +2648,11 @@
       </c>
       <c r="R32">
         <f t="shared" si="8"/>
-        <v>-8.830730158730178E-4</v>
+        <v>-8.8227022222222423E-4</v>
       </c>
       <c r="S32">
         <f t="shared" si="9"/>
-        <v>-8.0390095238095413E-4</v>
+        <v>-8.0317013333333512E-4</v>
       </c>
       <c r="W32" t="s">
         <v>24</v>
@@ -2691,11 +2714,11 @@
       </c>
       <c r="R33">
         <f t="shared" si="8"/>
-        <v>-1.5471500000000034E-3</v>
+        <v>-1.5457435000000035E-3</v>
       </c>
       <c r="S33">
         <f t="shared" si="9"/>
-        <v>-1.4084400000000032E-3</v>
+        <v>-1.4071596000000033E-3</v>
       </c>
       <c r="W33" t="s">
         <v>25</v>
@@ -2757,11 +2780,11 @@
       </c>
       <c r="R34">
         <f t="shared" si="8"/>
-        <v>-8.8509841269841468E-4</v>
+        <v>-8.8429377777777987E-4</v>
       </c>
       <c r="S34">
         <f t="shared" si="9"/>
-        <v>-8.0574476190476373E-4</v>
+        <v>-8.0501226666666859E-4</v>
       </c>
       <c r="W34" t="s">
         <v>26</v>
@@ -2823,7 +2846,7 @@
       </c>
       <c r="R35">
         <f t="shared" si="8"/>
-        <v>-5.5381944444444567E-3</v>
+        <v>-5.5331597222222353E-3</v>
       </c>
       <c r="S35">
         <f t="shared" si="9"/>
@@ -2889,7 +2912,7 @@
       </c>
       <c r="R36">
         <f t="shared" si="8"/>
-        <v>-3.7702761904761981E-3</v>
+        <v>-3.7668486666666747E-3</v>
       </c>
       <c r="S36">
         <f t="shared" si="9"/>
@@ -2955,7 +2978,7 @@
       </c>
       <c r="R37">
         <f t="shared" si="8"/>
-        <v>-6.6610238095238239E-4</v>
+        <v>-6.6549683333333475E-4</v>
       </c>
       <c r="S37">
         <f t="shared" si="9"/>
@@ -3021,7 +3044,7 @@
       </c>
       <c r="R38">
         <f t="shared" si="8"/>
-        <v>-4.4457460317460417E-4</v>
+        <v>-4.4417044444444546E-4</v>
       </c>
       <c r="S38">
         <f t="shared" si="9"/>
@@ -3087,7 +3110,7 @@
       </c>
       <c r="R39">
         <f t="shared" si="8"/>
-        <v>-9.5692404761904964E-3</v>
+        <v>-9.5605411666666879E-3</v>
       </c>
       <c r="S39">
         <f t="shared" si="9"/>
@@ -3153,7 +3176,7 @@
       </c>
       <c r="R40">
         <f t="shared" si="8"/>
-        <v>-3.1191111111111185E-3</v>
+        <v>-3.1162755555555633E-3</v>
       </c>
       <c r="S40">
         <f t="shared" si="9"/>
@@ -3219,7 +3242,7 @@
       </c>
       <c r="R41">
         <f t="shared" si="8"/>
-        <v>-6.6914047619047847E-4</v>
+        <v>-6.6853216666666897E-4</v>
       </c>
       <c r="S41">
         <f t="shared" si="9"/>
@@ -3285,7 +3308,7 @@
       </c>
       <c r="R42">
         <f t="shared" si="8"/>
-        <v>-2.679600000000009E-3</v>
+        <v>-2.6771640000000092E-3</v>
       </c>
       <c r="S42">
         <f t="shared" si="9"/>
@@ -3351,7 +3374,7 @@
       </c>
       <c r="R43">
         <f t="shared" si="8"/>
-        <v>-2.9061912698412789E-3</v>
+        <v>-2.9035492777777869E-3</v>
       </c>
       <c r="S43">
         <f t="shared" si="9"/>
@@ -3417,7 +3440,7 @@
       </c>
       <c r="R44">
         <f t="shared" si="8"/>
-        <v>-3.5809015873015993E-3</v>
+        <v>-3.5776462222222344E-3</v>
       </c>
       <c r="S44">
         <f t="shared" si="9"/>
@@ -3483,7 +3506,7 @@
       </c>
       <c r="R45">
         <f t="shared" si="8"/>
-        <v>-2.0165357142857207E-3</v>
+        <v>-2.0147025000000064E-3</v>
       </c>
       <c r="S45">
         <f t="shared" si="9"/>
@@ -3549,7 +3572,7 @@
       </c>
       <c r="R46">
         <f t="shared" si="8"/>
-        <v>-2.0188142857142928E-3</v>
+        <v>-2.0169790000000073E-3</v>
       </c>
       <c r="S46">
         <f t="shared" si="9"/>
@@ -3615,7 +3638,7 @@
       </c>
       <c r="R47">
         <f t="shared" si="8"/>
-        <v>-8.9826349206349515E-4</v>
+        <v>-8.9744688888889195E-4</v>
       </c>
       <c r="S47">
         <f t="shared" si="9"/>
@@ -3681,7 +3704,7 @@
       </c>
       <c r="R48">
         <f t="shared" si="8"/>
-        <v>-6.7445714285714489E-4</v>
+        <v>-6.7384400000000211E-4</v>
       </c>
       <c r="S48">
         <f t="shared" si="9"/>
@@ -3747,7 +3770,7 @@
       </c>
       <c r="R49">
         <f t="shared" si="8"/>
-        <v>-3.151011111111122E-3</v>
+        <v>-3.1481465555555665E-3</v>
       </c>
       <c r="S49">
         <f t="shared" si="9"/>
@@ -3813,7 +3836,7 @@
       </c>
       <c r="R50">
         <f t="shared" si="8"/>
-        <v>-6.9850873015873246E-3</v>
+        <v>-6.9787372222222454E-3</v>
       </c>
       <c r="S50">
         <f t="shared" si="9"/>
@@ -3879,7 +3902,7 @@
       </c>
       <c r="R51">
         <f t="shared" si="8"/>
-        <v>-5.1883071428571606E-3</v>
+        <v>-5.183590500000018E-3</v>
       </c>
       <c r="S51">
         <f t="shared" si="9"/>
@@ -3945,7 +3968,7 @@
       </c>
       <c r="R52">
         <f t="shared" si="8"/>
-        <v>-3.8391396825396959E-3</v>
+        <v>-3.835649555555569E-3</v>
       </c>
       <c r="S52">
         <f t="shared" si="9"/>
@@ -4011,7 +4034,7 @@
       </c>
       <c r="R53">
         <f t="shared" si="8"/>
-        <v>-2.4869341269841377E-3</v>
+        <v>-2.4846732777777888E-3</v>
       </c>
       <c r="S53">
         <f t="shared" si="9"/>
@@ -4077,7 +4100,7 @@
       </c>
       <c r="R54">
         <f t="shared" si="8"/>
-        <v>-1.3580285714285773E-3</v>
+        <v>-1.356794000000006E-3</v>
       </c>
       <c r="S54">
         <f t="shared" si="9"/>
@@ -4143,11 +4166,11 @@
       </c>
       <c r="R55">
         <f t="shared" si="8"/>
-        <v>-2.4925039682539792E-3</v>
+        <v>-2.4902380555555667E-3</v>
       </c>
       <c r="S55">
         <f t="shared" si="9"/>
-        <v>-2.2690380952381053E-3</v>
+        <v>-2.2669753333333436E-3</v>
       </c>
       <c r="W55" t="s">
         <v>46</v>
@@ -4209,11 +4232,11 @@
       </c>
       <c r="R56">
         <f t="shared" si="8"/>
-        <v>-1.8147555555555637E-3</v>
+        <v>-1.8131057777777862E-3</v>
       </c>
       <c r="S56">
         <f t="shared" si="9"/>
-        <v>-1.6520533333333404E-3</v>
+        <v>-1.6505514666666739E-3</v>
       </c>
       <c r="W56" t="s">
         <v>47</v>
@@ -4275,11 +4298,11 @@
       </c>
       <c r="R57">
         <f t="shared" si="8"/>
-        <v>-4.5419523809524004E-4</v>
+        <v>-4.5378233333333529E-4</v>
       </c>
       <c r="S57">
         <f t="shared" si="9"/>
-        <v>-4.1347428571428745E-4</v>
+        <v>-4.130984000000018E-4</v>
       </c>
       <c r="W57" t="s">
         <v>48</v>
@@ -4341,11 +4364,11 @@
       </c>
       <c r="R58">
         <f t="shared" si="8"/>
-        <v>-1.8188063492063573E-3</v>
+        <v>-1.817152888888897E-3</v>
       </c>
       <c r="S58">
         <f t="shared" si="9"/>
-        <v>-1.6557409523809596E-3</v>
+        <v>-1.6542357333333407E-3</v>
       </c>
       <c r="W58" t="s">
         <v>49</v>
@@ -4407,11 +4430,11 @@
       </c>
       <c r="R59">
         <f t="shared" si="8"/>
-        <v>-1.3656238095238157E-3</v>
+        <v>-1.3643823333333396E-3</v>
       </c>
       <c r="S59">
         <f t="shared" si="9"/>
-        <v>-1.2431885714285769E-3</v>
+        <v>-1.2420584000000054E-3</v>
       </c>
       <c r="W59" t="s">
         <v>50</v>
@@ -4473,11 +4496,11 @@
       </c>
       <c r="R60">
         <f t="shared" si="8"/>
-        <v>-2.734285714285726E-3</v>
+        <v>-2.7318000000000121E-3</v>
       </c>
       <c r="S60">
         <f t="shared" si="9"/>
-        <v>-2.4891428571428677E-3</v>
+        <v>-2.4868800000000107E-3</v>
       </c>
       <c r="W60" t="s">
         <v>51</v>
@@ -4539,11 +4562,11 @@
       </c>
       <c r="R61">
         <f t="shared" si="8"/>
-        <v>-1.5967722222222291E-3</v>
+        <v>-1.5953206111111182E-3</v>
       </c>
       <c r="S61">
         <f t="shared" si="9"/>
-        <v>-1.4536133333333397E-3</v>
+        <v>-1.4522918666666732E-3</v>
       </c>
       <c r="W61" t="s">
         <v>52</v>
@@ -4605,11 +4628,11 @@
       </c>
       <c r="R62">
         <f t="shared" si="8"/>
-        <v>-2.96872539682541E-3</v>
+        <v>-2.9660265555555691E-3</v>
       </c>
       <c r="S62">
         <f t="shared" si="9"/>
-        <v>-2.7025638095238215E-3</v>
+        <v>-2.7001069333333454E-3</v>
       </c>
       <c r="W62" t="s">
         <v>53</v>
@@ -4671,11 +4694,11 @@
       </c>
       <c r="R63">
         <f t="shared" si="8"/>
-        <v>-3.4292500000000143E-3</v>
+        <v>-3.4261325000000146E-3</v>
       </c>
       <c r="S63">
         <f t="shared" si="9"/>
-        <v>-3.1218000000000131E-3</v>
+        <v>-3.1189620000000133E-3</v>
       </c>
       <c r="W63" t="s">
         <v>54</v>
@@ -4737,11 +4760,11 @@
       </c>
       <c r="R64">
         <f t="shared" si="8"/>
-        <v>-1.5152761904761971E-2</v>
+        <v>-1.5138986666666734E-2</v>
       </c>
       <c r="S64">
         <f t="shared" si="9"/>
-        <v>-5.0004114285714498E-3</v>
+        <v>-4.9958656000000214E-3</v>
       </c>
       <c r="W64" t="s">
         <v>55</v>
@@ -4803,11 +4826,11 @@
       </c>
       <c r="R65">
         <f t="shared" si="8"/>
-        <v>-2.022603174603186E-2</v>
+        <v>-2.0207644444444558E-2</v>
       </c>
       <c r="S65">
         <f t="shared" si="9"/>
-        <v>-6.6745904761905126E-3</v>
+        <v>-6.6685226666667033E-3</v>
       </c>
       <c r="W65" t="s">
         <v>56</v>
@@ -4869,11 +4892,11 @@
       </c>
       <c r="R66">
         <f t="shared" si="8"/>
-        <v>-5.0620952380952657E-3</v>
+        <v>-5.0574933333333615E-3</v>
       </c>
       <c r="S66">
         <f t="shared" si="9"/>
-        <v>-1.6704914285714375E-3</v>
+        <v>-1.6689728000000091E-3</v>
       </c>
       <c r="W66" t="s">
         <v>57</v>
@@ -5001,11 +5024,11 @@
       </c>
       <c r="R68">
         <f t="shared" si="8"/>
-        <v>-1.0146539682539736E-2</v>
+        <v>-1.0137315555555609E-2</v>
       </c>
       <c r="S68">
         <f t="shared" si="9"/>
-        <v>-3.3483580952381126E-3</v>
+        <v>-3.3453141333333507E-3</v>
       </c>
       <c r="W68" t="s">
         <v>59</v>
@@ -5067,11 +5090,11 @@
       </c>
       <c r="R69">
         <f t="shared" si="8"/>
-        <v>-2.0950285714285831E-2</v>
+        <v>-2.0931240000000118E-2</v>
       </c>
       <c r="S69">
         <f t="shared" si="9"/>
-        <v>-6.9135942857143232E-3</v>
+        <v>-6.9073092000000377E-3</v>
       </c>
       <c r="W69" t="s">
         <v>60</v>
@@ -5133,11 +5156,11 @@
       </c>
       <c r="R70">
         <f t="shared" si="8"/>
-        <v>-6.3555555555555908E-3</v>
+        <v>-6.3497777777778135E-3</v>
       </c>
       <c r="S70">
         <f t="shared" si="9"/>
-        <v>-2.0973333333333447E-3</v>
+        <v>-2.0954266666666781E-3</v>
       </c>
       <c r="W70" t="s">
         <v>61</v>
@@ -5199,11 +5222,11 @@
       </c>
       <c r="R71">
         <f t="shared" si="8"/>
-        <v>-3.1812698412698594E-3</v>
+        <v>-3.1783777777777958E-3</v>
       </c>
       <c r="S71">
         <f t="shared" si="9"/>
-        <v>-1.0498190476190535E-3</v>
+        <v>-1.0488646666666724E-3</v>
       </c>
       <c r="W71" t="s">
         <v>62</v>
@@ -5265,11 +5288,11 @@
       </c>
       <c r="R72">
         <f t="shared" si="8"/>
-        <v>-1.6560761904761998E-2</v>
+        <v>-1.654570666666676E-2</v>
       </c>
       <c r="S72">
         <f t="shared" si="9"/>
-        <v>-5.4650514285714573E-3</v>
+        <v>-5.4600832000000297E-3</v>
       </c>
       <c r="W72" t="s">
         <v>63</v>
@@ -5331,11 +5354,11 @@
       </c>
       <c r="R73">
         <f t="shared" si="8"/>
-        <v>-1.6578920634920728E-2</v>
+        <v>-1.6563848888888982E-2</v>
       </c>
       <c r="S73">
         <f t="shared" si="9"/>
-        <v>-5.4710438095238395E-3</v>
+        <v>-5.4660701333333643E-3</v>
       </c>
       <c r="W73" t="s">
         <v>64</v>
@@ -5397,11 +5420,11 @@
       </c>
       <c r="R74">
         <f t="shared" si="8"/>
-        <v>-1.9150476190476296E-3</v>
+        <v>-1.9133066666666774E-3</v>
       </c>
       <c r="S74">
         <f t="shared" si="9"/>
-        <v>-6.3196571428571777E-4</v>
+        <v>-6.3139120000000346E-4</v>
       </c>
       <c r="W74" t="s">
         <v>65</v>
@@ -5463,11 +5486,11 @@
       </c>
       <c r="R75">
         <f t="shared" si="8"/>
-        <v>-2.3644761904762029E-2</v>
+        <v>-2.3623266666666792E-2</v>
       </c>
       <c r="S75">
         <f t="shared" si="9"/>
-        <v>-7.8027714285714691E-3</v>
+        <v>-7.7956780000000411E-3</v>
       </c>
       <c r="W75" t="s">
         <v>66</v>
@@ -5529,11 +5552,11 @@
       </c>
       <c r="R76">
         <f t="shared" ref="R76:R139" si="23">(J76*L76+K76*M76)*$N$11</f>
-        <v>-1.9192380952381058E-3</v>
+        <v>-1.9174933333333441E-3</v>
       </c>
       <c r="S76">
         <f t="shared" ref="S76:S139" si="24">I76*O76*P$11*Q$11*N$11</f>
-        <v>-6.3334857142857486E-4</v>
+        <v>-6.327728000000035E-4</v>
       </c>
       <c r="W76" t="s">
         <v>67</v>
@@ -5595,11 +5618,11 @@
       </c>
       <c r="R77">
         <f t="shared" si="23"/>
-        <v>-1.9213333333333461E-3</v>
+        <v>-1.9195866666666796E-3</v>
       </c>
       <c r="S77">
         <f t="shared" si="24"/>
-        <v>-6.3404000000000411E-4</v>
+        <v>-6.3346360000000412E-4</v>
       </c>
       <c r="W77" t="s">
         <v>68</v>
@@ -5661,11 +5684,11 @@
       </c>
       <c r="R78">
         <f t="shared" si="23"/>
-        <v>-6.4114285714286139E-3</v>
+        <v>-6.4056000000000425E-3</v>
       </c>
       <c r="S78">
         <f t="shared" si="24"/>
-        <v>-2.115771428571442E-3</v>
+        <v>-2.1138480000000136E-3</v>
       </c>
       <c r="W78" t="s">
         <v>69</v>
@@ -5727,7 +5750,7 @@
       </c>
       <c r="R79">
         <f t="shared" si="23"/>
-        <v>-1.604603174603185E-2</v>
+        <v>-1.6031444444444549E-2</v>
       </c>
       <c r="S79">
         <f t="shared" si="24"/>
@@ -5793,7 +5816,7 @@
       </c>
       <c r="R80">
         <f t="shared" si="23"/>
-        <v>-1.7348571428571543E-2</v>
+        <v>-1.7332800000000113E-2</v>
       </c>
       <c r="S80">
         <f t="shared" si="24"/>
@@ -5859,7 +5882,7 @@
       </c>
       <c r="R81">
         <f t="shared" si="23"/>
-        <v>-1.1578285714285789E-2</v>
+        <v>-1.1567760000000076E-2</v>
       </c>
       <c r="S81">
         <f t="shared" si="24"/>
@@ -5925,7 +5948,7 @@
       </c>
       <c r="R82">
         <f t="shared" si="23"/>
-        <v>-7.7272380952381446E-3</v>
+        <v>-7.7202133333333827E-3</v>
       </c>
       <c r="S82">
         <f t="shared" si="24"/>
@@ -5991,7 +6014,7 @@
       </c>
       <c r="R83">
         <f t="shared" si="23"/>
-        <v>-2.0628317460317593E-2</v>
+        <v>-2.0609564444444579E-2</v>
       </c>
       <c r="S83">
         <f t="shared" si="24"/>
@@ -6057,7 +6080,7 @@
       </c>
       <c r="R84">
         <f t="shared" si="23"/>
-        <v>-1.2906666666666754E-2</v>
+        <v>-1.2894933333333421E-2</v>
       </c>
       <c r="S84">
         <f t="shared" si="24"/>
@@ -6123,7 +6146,7 @@
       </c>
       <c r="R85">
         <f t="shared" si="23"/>
-        <v>-1.1628571428571502E-2</v>
+        <v>-1.1618000000000073E-2</v>
       </c>
       <c r="S85">
         <f t="shared" si="24"/>
@@ -6189,7 +6212,7 @@
       </c>
       <c r="R86">
         <f t="shared" si="23"/>
-        <v>-2.5869206349206517E-2</v>
+        <v>-2.5845688888889058E-2</v>
       </c>
       <c r="S86">
         <f t="shared" si="24"/>
@@ -6255,7 +6278,7 @@
       </c>
       <c r="R87">
         <f t="shared" si="23"/>
-        <v>-1.3596000000000087E-2</v>
+        <v>-1.3583640000000088E-2</v>
       </c>
       <c r="S87">
         <f t="shared" si="24"/>
@@ -6321,7 +6344,7 @@
       </c>
       <c r="R88">
         <f t="shared" si="23"/>
-        <v>-2.7221333333333535E-2</v>
+        <v>-2.7196586666666869E-2</v>
       </c>
       <c r="S88">
         <f t="shared" si="24"/>
@@ -6387,7 +6410,7 @@
       </c>
       <c r="R89">
         <f t="shared" si="23"/>
-        <v>-2.1411238095238257E-2</v>
+        <v>-2.1391773333333496E-2</v>
       </c>
       <c r="S89">
         <f t="shared" si="24"/>
@@ -6453,7 +6476,7 @@
       </c>
       <c r="R90">
         <f t="shared" si="23"/>
-        <v>-1.4289523809523915E-2</v>
+        <v>-1.427653333333344E-2</v>
       </c>
       <c r="S90">
         <f t="shared" si="24"/>
@@ -6519,7 +6542,7 @@
       </c>
       <c r="R91">
         <f t="shared" si="23"/>
-        <v>-4.5515555555555908E-3</v>
+        <v>-4.5474177777778124E-3</v>
       </c>
       <c r="S91">
         <f t="shared" si="24"/>
@@ -6585,7 +6608,7 @@
       </c>
       <c r="R92">
         <f t="shared" si="23"/>
-        <v>-2.0178539682539832E-2</v>
+        <v>-2.0160195555555708E-2</v>
       </c>
       <c r="S92">
         <f t="shared" si="24"/>
@@ -6651,7 +6674,7 @@
       </c>
       <c r="R93">
         <f t="shared" si="23"/>
-        <v>-1.7593714285714414E-2</v>
+        <v>-1.757772000000013E-2</v>
       </c>
       <c r="S93">
         <f t="shared" si="24"/>
@@ -6717,7 +6740,7 @@
       </c>
       <c r="R94">
         <f t="shared" si="23"/>
-        <v>-3.2615873015873265E-3</v>
+        <v>-3.2586222222222472E-3</v>
       </c>
       <c r="S94">
         <f t="shared" si="24"/>
@@ -6784,7 +6807,7 @@
       </c>
       <c r="R95">
         <f t="shared" si="23"/>
-        <v>-5.7791904761905193E-3</v>
+        <v>-5.77393666666671E-3</v>
       </c>
       <c r="S95">
         <f t="shared" si="24"/>
@@ -6851,7 +6874,7 @@
       </c>
       <c r="R96">
         <f t="shared" si="23"/>
-        <v>-6.3246857142857608E-3</v>
+        <v>-6.3189360000000467E-3</v>
       </c>
       <c r="S96">
         <f t="shared" si="24"/>
@@ -6918,7 +6941,7 @@
       </c>
       <c r="R97">
         <f t="shared" si="23"/>
-        <v>-1.3251857142857241E-3</v>
+        <v>-1.3239810000000099E-3</v>
       </c>
       <c r="S97">
         <f t="shared" si="24"/>
@@ -6985,7 +7008,7 @@
       </c>
       <c r="R98">
         <f t="shared" si="23"/>
-        <v>-1.3266000000000098E-3</v>
+        <v>-1.3253940000000099E-3</v>
       </c>
       <c r="S98">
         <f t="shared" si="24"/>
@@ -7046,11 +7069,11 @@
       </c>
       <c r="R99">
         <f t="shared" si="23"/>
-        <v>-2.0658000000000161E-3</v>
+        <v>-2.0639220000000162E-3</v>
       </c>
       <c r="S99">
         <f t="shared" si="24"/>
-        <v>-3.0298400000000232E-3</v>
+        <v>-3.0270856000000233E-3</v>
       </c>
     </row>
     <row r="100" spans="1:24" x14ac:dyDescent="0.2">
@@ -7107,11 +7130,11 @@
       </c>
       <c r="R100">
         <f t="shared" si="23"/>
-        <v>-1.9202857142857307E-3</v>
+        <v>-1.9185400000000163E-3</v>
       </c>
       <c r="S100">
         <f t="shared" si="24"/>
-        <v>-2.8164190476190711E-3</v>
+        <v>-2.8138586666666904E-3</v>
       </c>
     </row>
     <row r="101" spans="1:24" x14ac:dyDescent="0.2">
@@ -7168,11 +7191,11 @@
       </c>
       <c r="R101">
         <f t="shared" si="23"/>
-        <v>-4.5840142857143246E-3</v>
+        <v>-4.5798470000000396E-3</v>
       </c>
       <c r="S101">
         <f t="shared" si="24"/>
-        <v>-6.7232209523810094E-3</v>
+        <v>-6.7171089333333909E-3</v>
       </c>
     </row>
     <row r="102" spans="1:24" x14ac:dyDescent="0.2">
@@ -7229,11 +7252,11 @@
       </c>
       <c r="R102">
         <f t="shared" si="23"/>
-        <v>-1.4802857142857267E-4</v>
+        <v>-1.4789400000000125E-4</v>
       </c>
       <c r="S102">
         <f t="shared" si="24"/>
-        <v>-2.1710857142857328E-4</v>
+        <v>-2.1691120000000188E-4</v>
       </c>
     </row>
     <row r="103" spans="1:24" x14ac:dyDescent="0.2">
@@ -7290,11 +7313,11 @@
       </c>
       <c r="R103">
         <f t="shared" si="23"/>
-        <v>-1.0373000000000088E-3</v>
+        <v>-1.0363570000000088E-3</v>
       </c>
       <c r="S103">
         <f t="shared" si="24"/>
-        <v>-1.5213733333333461E-3</v>
+        <v>-1.5199902666666795E-3</v>
       </c>
     </row>
     <row r="104" spans="1:24" x14ac:dyDescent="0.2">
@@ -7351,11 +7374,11 @@
       </c>
       <c r="R104">
         <f t="shared" si="23"/>
-        <v>-8.9005714285715035E-4</v>
+        <v>-8.8924800000000752E-4</v>
       </c>
       <c r="S104">
         <f t="shared" si="24"/>
-        <v>-1.3054171428571537E-3</v>
+        <v>-1.304230400000011E-3</v>
       </c>
     </row>
     <row r="105" spans="1:24" x14ac:dyDescent="0.2">
@@ -7412,11 +7435,11 @@
       </c>
       <c r="R105">
         <f t="shared" si="23"/>
-        <v>-1.3365000000000113E-3</v>
+        <v>-1.3352850000000113E-3</v>
       </c>
       <c r="S105">
         <f t="shared" si="24"/>
-        <v>-1.9602000000000161E-3</v>
+        <v>-1.958418000000016E-3</v>
       </c>
     </row>
     <row r="106" spans="1:24" x14ac:dyDescent="0.2">
@@ -7473,11 +7496,11 @@
       </c>
       <c r="R106">
         <f t="shared" si="23"/>
-        <v>-2.8244857142857385E-3</v>
+        <v>-2.8219180000000244E-3</v>
       </c>
       <c r="S106">
         <f t="shared" si="24"/>
-        <v>-4.1425790476190827E-3</v>
+        <v>-4.1388130666667015E-3</v>
       </c>
     </row>
     <row r="107" spans="1:24" x14ac:dyDescent="0.2">
@@ -7534,11 +7557,11 @@
       </c>
       <c r="R107">
         <f t="shared" si="23"/>
-        <v>-1.9345857142857306E-3</v>
+        <v>-1.9328270000000163E-3</v>
       </c>
       <c r="S107">
         <f t="shared" si="24"/>
-        <v>-2.8373923809524048E-3</v>
+        <v>-2.8348129333333571E-3</v>
       </c>
     </row>
     <row r="108" spans="1:24" x14ac:dyDescent="0.2">
@@ -7595,11 +7618,11 @@
       </c>
       <c r="R108">
         <f t="shared" si="23"/>
-        <v>-5.9588571428571932E-4</v>
+        <v>-5.9534400000000503E-4</v>
       </c>
       <c r="S108">
         <f t="shared" si="24"/>
-        <v>-8.7396571428572159E-4</v>
+        <v>-8.7317120000000728E-4</v>
       </c>
     </row>
     <row r="109" spans="1:24" x14ac:dyDescent="0.2">
@@ -7656,11 +7679,11 @@
       </c>
       <c r="R109">
         <f t="shared" si="23"/>
-        <v>-5.9651428571429075E-3</v>
+        <v>-5.9597200000000503E-3</v>
       </c>
       <c r="S109">
         <f t="shared" si="24"/>
-        <v>-8.7488761904762642E-3</v>
+        <v>-8.7409226666667408E-3</v>
       </c>
     </row>
     <row r="110" spans="1:24" x14ac:dyDescent="0.2">
@@ -7717,11 +7740,11 @@
       </c>
       <c r="R110">
         <f t="shared" si="23"/>
-        <v>-1.3435714285714398E-3</v>
+        <v>-1.3423500000000112E-3</v>
       </c>
       <c r="S110">
         <f t="shared" si="24"/>
-        <v>-1.9705714285714448E-3</v>
+        <v>-1.9687800000000163E-3</v>
       </c>
     </row>
     <row r="111" spans="1:24" x14ac:dyDescent="0.2">
@@ -7778,11 +7801,11 @@
       </c>
       <c r="R111">
         <f t="shared" si="23"/>
-        <v>-5.9777142857143418E-4</v>
+        <v>-5.9722800000000574E-4</v>
       </c>
       <c r="S111">
         <f t="shared" si="24"/>
-        <v>-8.7673142857143686E-4</v>
+        <v>-8.7593440000000825E-4</v>
       </c>
     </row>
     <row r="112" spans="1:24" x14ac:dyDescent="0.2">
@@ -7839,11 +7862,11 @@
       </c>
       <c r="R112">
         <f t="shared" si="23"/>
-        <v>-2.1575644444444649E-2</v>
+        <v>-2.1556030222222425E-2</v>
       </c>
       <c r="S112">
         <f t="shared" si="24"/>
-        <v>-9.6541866666667569E-3</v>
+        <v>-9.6454101333334243E-3</v>
       </c>
     </row>
     <row r="113" spans="1:19" x14ac:dyDescent="0.2">
@@ -7900,11 +7923,11 @@
       </c>
       <c r="R113">
         <f t="shared" si="23"/>
-        <v>-1.0308283333333432E-2</v>
+        <v>-1.0298912166666766E-2</v>
       </c>
       <c r="S113">
         <f t="shared" si="24"/>
-        <v>-4.6125200000000435E-3</v>
+        <v>-4.6083268000000439E-3</v>
       </c>
     </row>
     <row r="114" spans="1:19" x14ac:dyDescent="0.2">
@@ -7961,11 +7984,11 @@
       </c>
       <c r="R114">
         <f t="shared" si="23"/>
-        <v>-1.0319100000000097E-2</v>
+        <v>-1.0309719000000097E-2</v>
       </c>
       <c r="S114">
         <f t="shared" si="24"/>
-        <v>-4.6173600000000417E-3</v>
+        <v>-4.6131624000000423E-3</v>
       </c>
     </row>
     <row r="115" spans="1:19" x14ac:dyDescent="0.2">
@@ -8022,11 +8045,11 @@
       </c>
       <c r="R115">
         <f t="shared" si="23"/>
-        <v>-9.3461150793651675E-3</v>
+        <v>-9.3376186111111988E-3</v>
       </c>
       <c r="S115">
         <f t="shared" si="24"/>
-        <v>-4.1819904761905159E-3</v>
+        <v>-4.1781886666667064E-3</v>
       </c>
     </row>
     <row r="116" spans="1:19" x14ac:dyDescent="0.2">
@@ -8083,11 +8106,11 @@
       </c>
       <c r="R116">
         <f t="shared" si="23"/>
-        <v>-1.9696634920635106E-3</v>
+        <v>-1.9678728888889076E-3</v>
       </c>
       <c r="S116">
         <f t="shared" si="24"/>
-        <v>-8.8134095238096065E-4</v>
+        <v>-8.805397333333417E-4</v>
       </c>
     </row>
     <row r="117" spans="1:19" x14ac:dyDescent="0.2">
@@ -8144,11 +8167,11 @@
       </c>
       <c r="R117">
         <f t="shared" si="23"/>
-        <v>-3.4505166666666995E-3</v>
+        <v>-3.4473798333333663E-3</v>
       </c>
       <c r="S117">
         <f t="shared" si="24"/>
-        <v>-1.5439600000000146E-3</v>
+        <v>-1.5425564000000147E-3</v>
       </c>
     </row>
     <row r="118" spans="1:19" x14ac:dyDescent="0.2">
@@ -8205,11 +8228,11 @@
       </c>
       <c r="R118">
         <f t="shared" si="23"/>
-        <v>-1.9737841269841455E-3</v>
+        <v>-1.9719897777777965E-3</v>
       </c>
       <c r="S118">
         <f t="shared" si="24"/>
-        <v>-8.8318476190477014E-4</v>
+        <v>-8.8238186666667496E-4</v>
       </c>
     </row>
     <row r="119" spans="1:19" x14ac:dyDescent="0.2">
@@ -8266,11 +8289,11 @@
       </c>
       <c r="R119">
         <f t="shared" si="23"/>
-        <v>-1.2349027777777894E-2</v>
+        <v>-1.2337801388889005E-2</v>
       </c>
       <c r="S119">
         <f t="shared" si="24"/>
-        <v>-5.5256666666667177E-3</v>
+        <v>-5.5206433333333848E-3</v>
       </c>
     </row>
     <row r="120" spans="1:19" x14ac:dyDescent="0.2">
@@ -8327,11 +8350,11 @@
       </c>
       <c r="R120">
         <f t="shared" si="23"/>
-        <v>-8.4060952380953166E-3</v>
+        <v>-8.3984533333334114E-3</v>
       </c>
       <c r="S120">
         <f t="shared" si="24"/>
-        <v>-3.7613714285714634E-3</v>
+        <v>-3.7579520000000349E-3</v>
       </c>
     </row>
     <row r="121" spans="1:19" x14ac:dyDescent="0.2">
@@ -8388,11 +8411,11 @@
       </c>
       <c r="R121">
         <f t="shared" si="23"/>
-        <v>-1.4849738095238235E-3</v>
+        <v>-1.4836238333333473E-3</v>
       </c>
       <c r="S121">
         <f t="shared" si="24"/>
-        <v>-6.6446285714286341E-4</v>
+        <v>-6.6385880000000626E-4</v>
       </c>
     </row>
     <row r="122" spans="1:19" x14ac:dyDescent="0.2">
@@ -8449,11 +8472,11 @@
       </c>
       <c r="R122">
         <f t="shared" si="23"/>
-        <v>-9.9101269841270754E-4</v>
+        <v>-9.9011177777778695E-4</v>
       </c>
       <c r="S122">
         <f t="shared" si="24"/>
-        <v>-4.4343619047619456E-4</v>
+        <v>-4.4303306666667079E-4</v>
       </c>
     </row>
     <row r="123" spans="1:19" x14ac:dyDescent="0.2">
@@ -8510,7 +8533,7 @@
       </c>
       <c r="R123">
         <f t="shared" si="23"/>
-        <v>-2.1328921428571651E-2</v>
+        <v>-2.1309531500000221E-2</v>
       </c>
       <c r="S123">
         <f t="shared" si="24"/>
@@ -8571,7 +8594,7 @@
       </c>
       <c r="R124">
         <f t="shared" si="23"/>
-        <v>-6.9515111111111832E-3</v>
+        <v>-6.9451915555556283E-3</v>
       </c>
       <c r="S124">
         <f t="shared" si="24"/>
@@ -8632,7 +8655,7 @@
       </c>
       <c r="R125">
         <f t="shared" si="23"/>
-        <v>-1.4911547619047773E-3</v>
+        <v>-1.4897991666666822E-3</v>
       </c>
       <c r="S125">
         <f t="shared" si="24"/>
@@ -8693,7 +8716,7 @@
       </c>
       <c r="R126">
         <f t="shared" si="23"/>
-        <v>-5.9708000000000616E-3</v>
+        <v>-5.9653720000000616E-3</v>
       </c>
       <c r="S126">
         <f t="shared" si="24"/>
@@ -8754,7 +8777,7 @@
       </c>
       <c r="R127">
         <f t="shared" si="23"/>
-        <v>-6.4750626984127653E-3</v>
+        <v>-6.4691762777778451E-3</v>
       </c>
       <c r="S127">
         <f t="shared" si="24"/>
@@ -8815,7 +8838,7 @@
       </c>
       <c r="R128">
         <f t="shared" si="23"/>
-        <v>-7.9775492063492905E-3</v>
+        <v>-7.9702968888889728E-3</v>
       </c>
       <c r="S128">
         <f t="shared" si="24"/>
@@ -8876,7 +8899,7 @@
       </c>
       <c r="R129">
         <f t="shared" si="23"/>
-        <v>-4.4920071428571889E-3</v>
+        <v>-4.4879235000000461E-3</v>
       </c>
       <c r="S129">
         <f t="shared" si="24"/>
@@ -8937,7 +8960,7 @@
       </c>
       <c r="R130">
         <f t="shared" si="23"/>
-        <v>-4.496642857142903E-3</v>
+        <v>-4.4925550000000465E-3</v>
       </c>
       <c r="S130">
         <f t="shared" si="24"/>
@@ -8998,7 +9021,7 @@
       </c>
       <c r="R131">
         <f t="shared" si="23"/>
-        <v>-2.0005682539682747E-3</v>
+        <v>-1.9987495555555761E-3</v>
       </c>
       <c r="S131">
         <f t="shared" si="24"/>
@@ -9059,7 +9082,7 @@
       </c>
       <c r="R132">
         <f t="shared" si="23"/>
-        <v>-1.5019714285714437E-3</v>
+        <v>-1.5006060000000152E-3</v>
       </c>
       <c r="S132">
         <f t="shared" si="24"/>
@@ -9120,7 +9143,7 @@
       </c>
       <c r="R133">
         <f t="shared" si="23"/>
-        <v>-2.140600000000022E-3</v>
+        <v>-2.1386540000000224E-3</v>
       </c>
       <c r="S133">
         <f t="shared" si="24"/>
@@ -9181,7 +9204,7 @@
       </c>
       <c r="R134">
         <f t="shared" si="23"/>
-        <v>-4.744771428571477E-3</v>
+        <v>-4.7404580000000489E-3</v>
       </c>
       <c r="S134">
         <f t="shared" si="24"/>
@@ -9242,7 +9265,7 @@
       </c>
       <c r="R135">
         <f t="shared" si="23"/>
-        <v>-3.523928571428611E-3</v>
+        <v>-3.5207250000000401E-3</v>
       </c>
       <c r="S135">
         <f t="shared" si="24"/>
@@ -9303,7 +9326,7 @@
       </c>
       <c r="R136">
         <f t="shared" si="23"/>
-        <v>-2.607314285714315E-3</v>
+        <v>-2.6049440000000296E-3</v>
       </c>
       <c r="S136">
         <f t="shared" si="24"/>
@@ -9364,7 +9387,7 @@
       </c>
       <c r="R137">
         <f t="shared" si="23"/>
-        <v>-1.6888142857143045E-3</v>
+        <v>-1.6872790000000189E-3</v>
       </c>
       <c r="S137">
         <f t="shared" si="24"/>
@@ -9425,7 +9448,7 @@
       </c>
       <c r="R138">
         <f t="shared" si="23"/>
-        <v>-9.22114285714296E-4</v>
+        <v>-9.2127600000001036E-4</v>
       </c>
       <c r="S138">
         <f t="shared" si="24"/>
@@ -9486,7 +9509,7 @@
       </c>
       <c r="R139">
         <f t="shared" si="23"/>
-        <v>-1.6922714285714472E-3</v>
+        <v>-1.6907330000000187E-3</v>
       </c>
       <c r="S139">
         <f t="shared" si="24"/>
@@ -9547,7 +9570,7 @@
       </c>
       <c r="R140">
         <f t="shared" ref="R140:R178" si="39">(J140*L140+K140*M140)*$N$11</f>
-        <v>-1.2320000000000137E-3</v>
+        <v>-1.2308800000000138E-3</v>
       </c>
       <c r="S140">
         <f t="shared" ref="S140:S178" si="40">I140*O140*P$11*Q$11*N$11</f>
@@ -9608,7 +9631,7 @@
       </c>
       <c r="R141">
         <f t="shared" si="39"/>
-        <v>-3.0831428571428921E-4</v>
+        <v>-3.0803400000000352E-4</v>
       </c>
       <c r="S141">
         <f t="shared" si="40"/>
@@ -9669,7 +9692,7 @@
       </c>
       <c r="R142">
         <f t="shared" si="39"/>
-        <v>-1.2345142857142994E-3</v>
+        <v>-1.2333920000000137E-3</v>
       </c>
       <c r="S142">
         <f t="shared" si="40"/>
@@ -9730,11 +9753,11 @@
       </c>
       <c r="R143">
         <f t="shared" si="39"/>
-        <v>-9.2682857142858163E-4</v>
+        <v>-9.2598600000001025E-4</v>
       </c>
       <c r="S143">
         <f t="shared" si="40"/>
-        <v>-1.3593485714285865E-3</v>
+        <v>-1.3581128000000151E-3</v>
       </c>
     </row>
     <row r="144" spans="1:19" x14ac:dyDescent="0.2">
@@ -9791,11 +9814,11 @@
       </c>
       <c r="R144">
         <f t="shared" si="39"/>
-        <v>-1.8555428571428777E-3</v>
+        <v>-1.8538560000000207E-3</v>
       </c>
       <c r="S144">
         <f t="shared" si="40"/>
-        <v>-2.7214628571428871E-3</v>
+        <v>-2.7189888000000301E-3</v>
       </c>
     </row>
     <row r="145" spans="1:19" x14ac:dyDescent="0.2">
@@ -9852,11 +9875,11 @@
       </c>
       <c r="R145">
         <f t="shared" si="39"/>
-        <v>-1.083500000000012E-3</v>
+        <v>-1.082515000000012E-3</v>
       </c>
       <c r="S145">
         <f t="shared" si="40"/>
-        <v>-1.5891333333333509E-3</v>
+        <v>-1.5876886666666842E-3</v>
       </c>
     </row>
     <row r="146" spans="1:19" x14ac:dyDescent="0.2">
@@ -9913,11 +9936,11 @@
       </c>
       <c r="R146">
         <f t="shared" si="39"/>
-        <v>-2.0142571428571673E-3</v>
+        <v>-2.0124260000000246E-3</v>
       </c>
       <c r="S146">
         <f t="shared" si="40"/>
-        <v>-2.9542438095238452E-3</v>
+        <v>-2.951558133333369E-3</v>
       </c>
     </row>
     <row r="147" spans="1:19" x14ac:dyDescent="0.2">
@@ -9974,11 +9997,11 @@
       </c>
       <c r="R147">
         <f t="shared" si="39"/>
-        <v>-2.3265000000000282E-3</v>
+        <v>-2.3243850000000286E-3</v>
       </c>
       <c r="S147">
         <f t="shared" si="40"/>
-        <v>-3.412200000000041E-3</v>
+        <v>-3.4090980000000409E-3</v>
       </c>
     </row>
     <row r="148" spans="1:19" x14ac:dyDescent="0.2">
@@ -10035,11 +10058,11 @@
       </c>
       <c r="R148">
         <f t="shared" si="39"/>
-        <v>-3.7261714285714734E-3</v>
+        <v>-3.7227840000000449E-3</v>
       </c>
       <c r="S148">
         <f t="shared" si="40"/>
-        <v>-5.4650514285714945E-3</v>
+        <v>-5.4600832000000661E-3</v>
       </c>
     </row>
     <row r="149" spans="1:19" x14ac:dyDescent="0.2">
@@ -10096,11 +10119,11 @@
       </c>
       <c r="R149">
         <f t="shared" si="39"/>
-        <v>-4.9732571428572027E-3</v>
+        <v>-4.9687360000000604E-3</v>
       </c>
       <c r="S149">
         <f t="shared" si="40"/>
-        <v>-7.2941104761905639E-3</v>
+        <v>-7.2874794666667542E-3</v>
       </c>
     </row>
     <row r="150" spans="1:19" x14ac:dyDescent="0.2">
@@ -10157,11 +10180,11 @@
       </c>
       <c r="R150">
         <f t="shared" si="39"/>
-        <v>-1.2445714285714436E-3</v>
+        <v>-1.2434400000000151E-3</v>
       </c>
       <c r="S150">
         <f t="shared" si="40"/>
-        <v>-1.8253714285714504E-3</v>
+        <v>-1.823712000000022E-3</v>
       </c>
     </row>
     <row r="151" spans="1:19" x14ac:dyDescent="0.2">
@@ -10279,11 +10302,11 @@
       </c>
       <c r="R152">
         <f t="shared" si="39"/>
-        <v>-2.4941714285714586E-3</v>
+        <v>-2.49190400000003E-3</v>
       </c>
       <c r="S152">
         <f t="shared" si="40"/>
-        <v>-3.6581180952381387E-3</v>
+        <v>-3.6547925333333771E-3</v>
       </c>
     </row>
     <row r="153" spans="1:19" x14ac:dyDescent="0.2">
@@ -10340,11 +10363,11 @@
       </c>
       <c r="R153">
         <f t="shared" si="39"/>
-        <v>-5.1494142857143477E-3</v>
+        <v>-5.1447330000000627E-3</v>
       </c>
       <c r="S153">
         <f t="shared" si="40"/>
-        <v>-7.5524742857143766E-3</v>
+        <v>-7.5456084000000909E-3</v>
       </c>
     </row>
     <row r="154" spans="1:19" x14ac:dyDescent="0.2">
@@ -10401,11 +10424,11 @@
       </c>
       <c r="R154">
         <f t="shared" si="39"/>
-        <v>-1.5620000000000189E-3</v>
+        <v>-1.5605800000000189E-3</v>
       </c>
       <c r="S154">
         <f t="shared" si="40"/>
-        <v>-2.2909333333333611E-3</v>
+        <v>-2.2888506666666943E-3</v>
       </c>
     </row>
     <row r="155" spans="1:19" x14ac:dyDescent="0.2">
@@ -10462,11 +10485,11 @@
       </c>
       <c r="R155">
         <f t="shared" si="39"/>
-        <v>-7.8178571428572368E-4</v>
+        <v>-7.8107500000000943E-4</v>
       </c>
       <c r="S155">
         <f t="shared" si="40"/>
-        <v>-1.1466190476190615E-3</v>
+        <v>-1.1455766666666806E-3</v>
       </c>
     </row>
     <row r="156" spans="1:19" x14ac:dyDescent="0.2">
@@ -10523,11 +10546,11 @@
       </c>
       <c r="R156">
         <f t="shared" si="39"/>
-        <v>-4.0693714285714774E-3</v>
+        <v>-4.0656720000000496E-3</v>
       </c>
       <c r="S156">
         <f t="shared" si="40"/>
-        <v>-5.9684114285714993E-3</v>
+        <v>-5.962985600000071E-3</v>
       </c>
     </row>
     <row r="157" spans="1:19" x14ac:dyDescent="0.2">
@@ -10584,11 +10607,11 @@
       </c>
       <c r="R157">
         <f t="shared" si="39"/>
-        <v>-4.0734571428571913E-3</v>
+        <v>-4.0697540000000487E-3</v>
       </c>
       <c r="S157">
         <f t="shared" si="40"/>
-        <v>-5.9744038095238807E-3</v>
+        <v>-5.9689725333334047E-3</v>
       </c>
     </row>
     <row r="158" spans="1:19" x14ac:dyDescent="0.2">
@@ -10645,11 +10668,11 @@
       </c>
       <c r="R158">
         <f t="shared" si="39"/>
-        <v>-4.7048571428572034E-4</v>
+        <v>-4.700580000000061E-4</v>
       </c>
       <c r="S158">
         <f t="shared" si="40"/>
-        <v>-6.9004571428572315E-4</v>
+        <v>-6.8941840000000894E-4</v>
       </c>
     </row>
     <row r="159" spans="1:19" x14ac:dyDescent="0.2">
@@ -10706,11 +10729,11 @@
       </c>
       <c r="R159">
         <f t="shared" si="39"/>
-        <v>-5.8084714285715029E-3</v>
+        <v>-5.8031910000000747E-3</v>
       </c>
       <c r="S159">
         <f t="shared" si="40"/>
-        <v>-8.5190914285715354E-3</v>
+        <v>-8.5113468000001073E-3</v>
       </c>
     </row>
     <row r="160" spans="1:19" x14ac:dyDescent="0.2">
@@ -10767,11 +10790,11 @@
       </c>
       <c r="R160">
         <f t="shared" si="39"/>
-        <v>-4.7142857142857609E-4</v>
+        <v>-4.7100000000000467E-4</v>
       </c>
       <c r="S160">
         <f t="shared" si="40"/>
-        <v>-6.9142857142857829E-4</v>
+        <v>-6.9080000000000682E-4</v>
       </c>
     </row>
     <row r="161" spans="1:19" x14ac:dyDescent="0.2">
@@ -10828,11 +10851,11 @@
       </c>
       <c r="R161">
         <f t="shared" si="39"/>
-        <v>-4.7190000000000464E-4</v>
+        <v>-4.7147100000000466E-4</v>
       </c>
       <c r="S161">
         <f t="shared" si="40"/>
-        <v>-6.9212000000000689E-4</v>
+        <v>-6.9149080000000689E-4</v>
       </c>
     </row>
     <row r="162" spans="1:19" x14ac:dyDescent="0.2">
@@ -10889,11 +10912,11 @@
       </c>
       <c r="R162">
         <f t="shared" si="39"/>
-        <v>-1.5745714285714443E-3</v>
+        <v>-1.5731400000000158E-3</v>
       </c>
       <c r="S162">
         <f t="shared" si="40"/>
-        <v>-2.3093714285714519E-3</v>
+        <v>-2.3072720000000234E-3</v>
       </c>
     </row>
     <row r="163" spans="1:19" x14ac:dyDescent="0.2">
@@ -10950,11 +10973,11 @@
       </c>
       <c r="R163">
         <f t="shared" si="39"/>
-        <v>-3.940357142857182E-3</v>
+        <v>-3.936775000000039E-3</v>
       </c>
       <c r="S163">
         <f t="shared" si="40"/>
-        <v>-5.7791904761905332E-3</v>
+        <v>-5.7739366666667239E-3</v>
       </c>
     </row>
     <row r="164" spans="1:19" x14ac:dyDescent="0.2">
@@ -11011,11 +11034,11 @@
       </c>
       <c r="R164">
         <f t="shared" si="39"/>
-        <v>-4.2598285714286139E-3</v>
+        <v>-4.2559560000000425E-3</v>
       </c>
       <c r="S164">
         <f t="shared" si="40"/>
-        <v>-6.2477485714286336E-3</v>
+        <v>-6.2420688000000626E-3</v>
       </c>
     </row>
     <row r="165" spans="1:19" x14ac:dyDescent="0.2">
@@ -11072,11 +11095,11 @@
       </c>
       <c r="R165">
         <f t="shared" si="39"/>
-        <v>-2.8427142857143138E-3</v>
+        <v>-2.8401300000000279E-3</v>
       </c>
       <c r="S165">
         <f t="shared" si="40"/>
-        <v>-4.1693142857143258E-3</v>
+        <v>-4.1655240000000402E-3</v>
       </c>
     </row>
     <row r="166" spans="1:19" x14ac:dyDescent="0.2">
@@ -11133,11 +11156,11 @@
       </c>
       <c r="R166">
         <f t="shared" si="39"/>
-        <v>-1.8970285714285902E-3</v>
+        <v>-1.8953040000000189E-3</v>
       </c>
       <c r="S166">
         <f t="shared" si="40"/>
-        <v>-2.7823085714285983E-3</v>
+        <v>-2.779779200000027E-3</v>
       </c>
     </row>
     <row r="167" spans="1:19" x14ac:dyDescent="0.2">
@@ -11194,7 +11217,7 @@
       </c>
       <c r="R167">
         <f t="shared" si="39"/>
-        <v>-5.0637714285714777E-3</v>
+        <v>-5.0591680000000496E-3</v>
       </c>
       <c r="S167">
         <f t="shared" si="40"/>
@@ -11255,7 +11278,7 @@
       </c>
       <c r="R168">
         <f t="shared" si="39"/>
-        <v>-3.1680000000000315E-3</v>
+        <v>-3.1651200000000312E-3</v>
       </c>
       <c r="S168">
         <f t="shared" si="40"/>
@@ -11316,7 +11339,7 @@
       </c>
       <c r="R169">
         <f t="shared" si="39"/>
-        <v>-2.8540285714286E-3</v>
+        <v>-2.8514340000000285E-3</v>
       </c>
       <c r="S169">
         <f t="shared" si="40"/>
@@ -11377,7 +11400,7 @@
       </c>
       <c r="R170">
         <f t="shared" si="39"/>
-        <v>-6.3485714285714916E-3</v>
+        <v>-6.3428000000000633E-3</v>
       </c>
       <c r="S170">
         <f t="shared" si="40"/>
@@ -11438,7 +11461,7 @@
       </c>
       <c r="R171">
         <f t="shared" si="39"/>
-        <v>-3.3363000000000329E-3</v>
+        <v>-3.333267000000033E-3</v>
       </c>
       <c r="S171">
         <f t="shared" si="40"/>
@@ -11499,7 +11522,7 @@
       </c>
       <c r="R172">
         <f t="shared" si="39"/>
-        <v>-6.6792000000000665E-3</v>
+        <v>-6.6731280000000663E-3</v>
       </c>
       <c r="S172">
         <f t="shared" si="40"/>
@@ -11560,7 +11583,7 @@
       </c>
       <c r="R173">
         <f t="shared" si="39"/>
-        <v>-5.2531285714286242E-3</v>
+        <v>-5.2483530000000528E-3</v>
       </c>
       <c r="S173">
         <f t="shared" si="40"/>
@@ -11621,7 +11644,7 @@
       </c>
       <c r="R174">
         <f t="shared" si="39"/>
-        <v>-3.5055428571428913E-3</v>
+        <v>-3.5023560000000346E-3</v>
       </c>
       <c r="S174">
         <f t="shared" si="40"/>
@@ -11682,7 +11705,7 @@
       </c>
       <c r="R175">
         <f t="shared" si="39"/>
-        <v>-1.1165000000000109E-3</v>
+        <v>-1.1154850000000111E-3</v>
       </c>
       <c r="S175">
         <f t="shared" si="40"/>
@@ -11743,7 +11766,7 @@
       </c>
       <c r="R176">
         <f t="shared" si="39"/>
-        <v>-4.9493714285714771E-3</v>
+        <v>-4.9448720000000489E-3</v>
       </c>
       <c r="S176">
         <f t="shared" si="40"/>
@@ -11804,7 +11827,7 @@
       </c>
       <c r="R177">
         <f t="shared" si="39"/>
-        <v>-4.3149857142857559E-3</v>
+        <v>-4.311063000000042E-3</v>
       </c>
       <c r="S177">
         <f t="shared" si="40"/>
@@ -11865,7 +11888,7 @@
       </c>
       <c r="R178">
         <f t="shared" si="39"/>
-        <v>-7.9985714285715065E-4</v>
+        <v>-7.9913000000000792E-4</v>
       </c>
       <c r="S178">
         <f t="shared" si="40"/>
